--- a/spreadsheet/testdata/simple-2.xlsx
+++ b/spreadsheet/testdata/simple-2.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ma:workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xml="http://www.w3.org/XML/1998/namespace">
+<ma:workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <ma:sheets>
     <ma:sheet name="Sheet 1" sheetId="1" r:id="rId3"/>
   </ma:sheets>
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ma:sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xml="http://www.w3.org/XML/1998/namespace" count="1" uniqueCount="1">
+<ma:sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1" uniqueCount="1">
   <ma:si>
     <ma:t>Hello World!</ma:t>
   </ma:si>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<ma:styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xml="http://www.w3.org/XML/1998/namespace">
+<ma:styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <ma:fonts count="1">
     <ma:font>
       <ma:name val="Calibri"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ma:worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xml="http://www.w3.org/XML/1998/namespace">
+<ma:worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ma="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <ma:dimension ref="A1:A1"/>
   <ma:sheetData>
     <ma:row r="1">
